--- a/plate3d/PLATE3D_TURRET.xlsx
+++ b/plate3d/PLATE3D_TURRET.xlsx
@@ -1779,7 +1779,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>11</v>
       </c>
@@ -1806,6 +1806,9 @@
       </c>
       <c r="I46" t="s">
         <v>73</v>
+      </c>
+      <c r="J46">
+        <v>-90</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">

--- a/plate3d/PLATE3D_TURRET.xlsx
+++ b/plate3d/PLATE3D_TURRET.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="93">
   <si>
     <t>Turret - after Billy Hau, billyhau.hk</t>
   </si>
@@ -221,6 +221,18 @@
   </si>
   <si>
     <t>XY</t>
+  </si>
+  <si>
+    <t>pl.bs.e_1</t>
+  </si>
+  <si>
+    <t>pl.bs.e_2</t>
+  </si>
+  <si>
+    <t>pl.st.e_1</t>
+  </si>
+  <si>
+    <t>pl.st.e_2</t>
   </si>
   <si>
     <t>BASE</t>
@@ -1363,7 +1375,7 @@
         <v>68</v>
       </c>
       <c r="D30" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="E30" t="s">
         <v>19</v>
@@ -1392,7 +1404,7 @@
         <v>68</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
@@ -1459,7 +1471,7 @@
         <v>68</v>
       </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
@@ -1488,7 +1500,7 @@
         <v>68</v>
       </c>
       <c r="D34" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
@@ -1555,7 +1567,7 @@
         <v>68</v>
       </c>
       <c r="D36" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E36" t="s">
         <v>13</v>
@@ -1604,13 +1616,13 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C39" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D39" t="s">
         <v>23</v>
@@ -1628,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -1639,7 +1651,7 @@
         <v>67</v>
       </c>
       <c r="C40" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D40" t="s">
         <v>30</v>
@@ -1671,10 +1683,10 @@
         <v>67</v>
       </c>
       <c r="C41" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D41" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E41" t="s">
         <v>23</v>
@@ -1723,13 +1735,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C44" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D44" t="s">
         <v>24</v>
@@ -1747,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -1758,7 +1770,7 @@
         <v>67</v>
       </c>
       <c r="C45" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D45" t="s">
         <v>25</v>
@@ -1776,7 +1788,7 @@
         <v>2.5</v>
       </c>
       <c r="I45" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -1787,7 +1799,7 @@
         <v>67</v>
       </c>
       <c r="C46" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D46" t="s">
         <v>41</v>
@@ -1805,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J46">
         <v>-90</v>
@@ -1819,10 +1831,10 @@
         <v>67</v>
       </c>
       <c r="C47" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D47" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E47" t="s">
         <v>24</v>
@@ -1836,25 +1848,25 @@
         <v>11</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C49" t="s">
         <v>2</v>
       </c>
       <c r="D49" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E49" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F49" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G49" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H49" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -1862,16 +1874,16 @@
         <v>11</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C50" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D50" t="s">
         <v>68</v>
       </c>
       <c r="E50" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -1888,16 +1900,16 @@
         <v>11</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C52" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D52" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E52" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -1914,16 +1926,16 @@
         <v>11</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C54" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D54" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E54" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F54">
         <v>17.5</v>
@@ -1940,11 +1952,11 @@
         <v>11</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/plate3d/PLATE3D_TURRET.xlsx
+++ b/plate3d/PLATE3D_TURRET.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="101">
   <si>
     <t>Turret - after Billy Hau, billyhau.hk</t>
   </si>
@@ -287,6 +287,30 @@
   </si>
   <si>
     <t>as.canon</t>
+  </si>
+  <si>
+    <t>VIEW</t>
+  </si>
+  <si>
+    <t>ISO</t>
+  </si>
+  <si>
+    <t>TURRET - ISOMETRIC</t>
+  </si>
+  <si>
+    <t>PLOT</t>
+  </si>
+  <si>
+    <t>PART</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>PLATES</t>
+  </si>
+  <si>
+    <t>SECTIONS</t>
   </si>
   <si>
     <t>END</t>
@@ -683,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -971,6 +995,7 @@
         <v>15</v>
       </c>
     </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>11</v>
@@ -1011,6 +1036,7 @@
         <v>15</v>
       </c>
     </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>31</v>
@@ -1093,6 +1119,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>43</v>
@@ -1179,6 +1206,7 @@
         <v>5</v>
       </c>
     </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>11</v>
@@ -1297,6 +1325,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>11</v>
@@ -1576,6 +1605,7 @@
         <v>16</v>
       </c>
     </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>11</v>
@@ -1695,6 +1725,7 @@
         <v>16</v>
       </c>
     </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>11</v>
@@ -1843,6 +1874,7 @@
         <v>16</v>
       </c>
     </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>11</v>
@@ -1895,6 +1927,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>11</v>
@@ -1921,6 +1954,7 @@
         <v>45</v>
       </c>
     </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>11</v>
@@ -1947,12 +1981,64 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B56" s="3" t="s">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
         <v>92</v>
+      </c>
+      <c r="C56" t="s">
+        <v>88</v>
+      </c>
+      <c r="D56" t="s">
+        <v>93</v>
+      </c>
+      <c r="G56">
+        <v>50</v>
+      </c>
+      <c r="H56" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>95</v>
+      </c>
+      <c r="C57" t="s">
+        <v>96</v>
+      </c>
+      <c r="D57" t="s">
+        <v>97</v>
+      </c>
+      <c r="E57">
+        <v>10</v>
+      </c>
+      <c r="F57" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>95</v>
+      </c>
+      <c r="C58" t="s">
+        <v>40</v>
+      </c>
+      <c r="D58" t="s">
+        <v>97</v>
+      </c>
+      <c r="E58">
+        <v>20</v>
+      </c>
+      <c r="F58" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/plate3d/PLATE3D_TURRET.xlsx
+++ b/plate3d/PLATE3D_TURRET.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="93">
   <si>
     <t>Turret - after Billy Hau, billyhau.hk</t>
   </si>
@@ -287,30 +287,6 @@
   </si>
   <si>
     <t>as.canon</t>
-  </si>
-  <si>
-    <t>VIEW</t>
-  </si>
-  <si>
-    <t>ISO</t>
-  </si>
-  <si>
-    <t>TURRET - ISOMETRIC</t>
-  </si>
-  <si>
-    <t>PLOT</t>
-  </si>
-  <si>
-    <t>PART</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>PLATES</t>
-  </si>
-  <si>
-    <t>SECTIONS</t>
   </si>
   <si>
     <t>END</t>
@@ -707,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -995,7 +971,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>11</v>
@@ -1036,7 +1011,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>31</v>
@@ -1119,7 +1093,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>43</v>
@@ -1206,7 +1179,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>11</v>
@@ -1325,7 +1297,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>11</v>
@@ -1605,7 +1576,6 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>11</v>
@@ -1725,7 +1695,6 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>11</v>
@@ -1874,7 +1843,6 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>11</v>
@@ -1927,7 +1895,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>11</v>
@@ -1954,7 +1921,6 @@
         <v>45</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>11</v>
@@ -1981,64 +1947,12 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B56" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="C56" t="s">
-        <v>88</v>
-      </c>
-      <c r="D56" t="s">
-        <v>93</v>
-      </c>
-      <c r="G56">
-        <v>50</v>
-      </c>
-      <c r="H56" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B57" t="s">
-        <v>95</v>
-      </c>
-      <c r="C57" t="s">
-        <v>96</v>
-      </c>
-      <c r="D57" t="s">
-        <v>97</v>
-      </c>
-      <c r="E57">
-        <v>10</v>
-      </c>
-      <c r="F57" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B58" t="s">
-        <v>95</v>
-      </c>
-      <c r="C58" t="s">
-        <v>40</v>
-      </c>
-      <c r="D58" t="s">
-        <v>97</v>
-      </c>
-      <c r="E58">
-        <v>20</v>
-      </c>
-      <c r="F58" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
